--- a/reports/pdf_change_20260724.xlsx
+++ b/reports/pdf_change_20260724.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,207억   ·   현금 30억(0.7%)      당일 2026-07-24  vs  전영업일 2026-07-23      매수 3종목  /  매도 5종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,394억   ·   현금 30억(0.7%)      당일 2026-07-24  vs  전영업일 2026-07-23      매수 3종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>115</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>489479675</v>
+        <v>490467525</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-20</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-258452800</v>
+        <v>-258974400</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>20</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>895864000</v>
+        <v>897672000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-14</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-450905000</v>
+        <v>-451815000</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>404922600</v>
+        <v>405739800</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-8</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-224758800</v>
+        <v>-225212400</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>-5</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-763565500</v>
+        <v>-765106500</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>-5</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-417706500</v>
+        <v>-418549500</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
     <row r="12" ht="19" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,697억   ·   현금 14억(0.4%)      당일 2026-07-24  vs  전영업일 2026-07-23      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,701억   ·   현금 14억(0.4%)      당일 2026-07-24  vs  전영업일 2026-07-23      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B12" s="4" t="n"/>
@@ -875,7 +875,7 @@
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,423억   ·   현금 36억(1.4%)      당일 2026-07-24  vs  전영업일 2026-07-23      매수 2종목  /  매도 1종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,527억   ·   현금 37억(1.4%)      당일 2026-07-24  vs  전영업일 2026-07-23      매수 2종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B15" s="4" t="n"/>
@@ -971,7 +971,7 @@
         <v>25</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>453675000</v>
+        <v>456962500</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>-20</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-2126580000</v>
+        <v>-2141990000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>9</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>3154680000</v>
+        <v>3177540000</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,183억   ·   현금 24억(1.0%)      당일 2026-07-24  vs  전영업일 2026-07-23      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,244억   ·   현금 24억(1.0%)      당일 2026-07-24  vs  전영업일 2026-07-23      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1060,7 +1060,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 274억   ·   현금 0억(0.2%)      당일 2026-07-24  vs  전영업일 2026-07-23      매수 3종목  /  매도 2종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 290억   ·   현금 0억(0.1%)      당일 2026-07-24  vs  전영업일 2026-07-23      매수 3종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1156,11 +1156,11 @@
         <v>33</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>118377600</v>
+        <v>131670000</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>0.43%→0.86%</t>
+          <t>0.45%→0.91%</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
@@ -1177,11 +1177,11 @@
         <v>-139</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-38347320</v>
+        <v>-42414460</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>2.75%→2.60%</t>
+          <t>2.88%→2.72%</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
@@ -1200,11 +1200,11 @@
         <v>15</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>93594000</v>
+        <v>93024000</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>3.20%→3.53%</t>
+          <t>3.01%→3.32%</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
@@ -1221,11 +1221,11 @@
         <v>-56</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-154280000</v>
+        <v>-180880000</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>7.50%→6.92%</t>
+          <t>8.32%→7.68%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
@@ -1244,11 +1244,11 @@
         <v>5</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>59470000</v>
+        <v>58558000</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>2.90%→3.11%</t>
+          <t>2.70%→2.90%</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
@@ -1265,7 +1265,7 @@
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 456억   ·   현금 5억(1.0%)      당일 2026-07-24  vs  전영업일 2026-07-23      매수 0종목  /  매도 2종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 484억   ·   현금 5억(1.0%)      당일 2026-07-24  vs  전영업일 2026-07-23      매수 0종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
@@ -1366,7 +1366,7 @@
         <v>-15</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-191184000</v>
+        <v>-189477000</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>-8</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-274624000</v>
+        <v>-272172000</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>

--- a/reports/pdf_change_20260724.xlsx
+++ b/reports/pdf_change_20260724.xlsx
@@ -800,23 +800,23 @@
       <c r="E9" s="17" t="n"/>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-765106500</v>
+        <v>-418549500</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>8.29%→7.65%</t>
+          <t>0.46%→0.38%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>223→218</t>
+          <t>25→20</t>
         </is>
       </c>
     </row>
@@ -828,23 +828,23 @@
       <c r="E10" s="17" t="n"/>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-418549500</v>
+        <v>-765106500</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>0.46%→0.38%</t>
+          <t>8.29%→7.65%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>25→20</t>
+          <t>223→218</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20260724.xlsx
+++ b/reports/pdf_change_20260724.xlsx
@@ -800,23 +800,23 @@
       <c r="E9" s="17" t="n"/>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-418549500</v>
+        <v>-765106500</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>0.46%→0.38%</t>
+          <t>8.29%→7.65%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>25→20</t>
+          <t>223→218</t>
         </is>
       </c>
     </row>
@@ -828,23 +828,23 @@
       <c r="E10" s="17" t="n"/>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-765106500</v>
+        <v>-418549500</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>8.29%→7.65%</t>
+          <t>0.46%→0.38%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>223→218</t>
+          <t>25→20</t>
         </is>
       </c>
     </row>
